--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/dataset_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/dataset_summary.xlsx
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D64" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D65" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66">
